--- a/data/config/luban/config/general/develop.xlsx
+++ b/data/config/luban/config/general/develop.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="14250" windowHeight="7545"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -30,24 +30,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
   <si>
     <t>##var</t>
   </si>
   <si>
-    <t>item_template_id</t>
+    <t>id</t>
   </si>
   <si>
-    <t>#name</t>
+    <t>develop_system_type</t>
   </si>
   <si>
-    <t>item_type</t>
+    <t>develop_sub_type</t>
   </si>
   <si>
-    <t>stacked</t>
+    <t>max_level</t>
   </si>
   <si>
-    <t>squares</t>
+    <t>develop_reset_type</t>
   </si>
   <si>
     <t>##type</t>
@@ -56,22 +56,7 @@
     <t>int</t>
   </si>
   <si>
-    <t>bool</t>
-  </si>
-  <si>
     <t>##</t>
-  </si>
-  <si>
-    <t>物品编号</t>
-  </si>
-  <si>
-    <t>物品名称</t>
-  </si>
-  <si>
-    <t>物品类型</t>
-  </si>
-  <si>
-    <t>金币</t>
   </si>
 </sst>
 </file>
@@ -1297,39 +1282,42 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" spans="1:6">
       <c r="B4" s="2">
         <v>10001</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
+      <c r="C4" s="2">
+        <v>0</v>
       </c>
       <c r="D4" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>100</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1348,7 +1336,7 @@
   <conditionalFormatting sqref="B4">
     <cfRule type="duplicateValues" dxfId="0" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B3 B5:B1048576">
+  <conditionalFormatting sqref="B1:B2 B5:B1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="89"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/config/luban/config/general/develop.xlsx
+++ b/data/config/luban/config/general/develop.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="14250" windowHeight="7545"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -1308,10 +1308,10 @@
         <v>10001</v>
       </c>
       <c r="C4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2">
         <v>100</v>

--- a/data/config/luban/config/general/develop.xlsx
+++ b/data/config/luban/config/general/develop.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
   <si>
     <t>##var</t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t>develop_reset_type</t>
+  </si>
+  <si>
+    <t>refund_proportion</t>
   </si>
   <si>
     <t>##type</t>
@@ -1244,18 +1247,19 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="32.8833333333333" style="2" customWidth="1"/>
     <col min="2" max="2" width="18.125" style="2" customWidth="1"/>
     <col min="3" max="3" width="29.75" style="2" customWidth="1"/>
     <col min="4" max="5" width="26" style="2" customWidth="1"/>
     <col min="6" max="6" width="40.375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="7" max="7" width="19.875" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1274,13 +1278,16 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:6">
+    <row r="2" s="1" customFormat="1" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
@@ -1289,21 +1296,24 @@
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:6">
+    <row r="4" s="2" customFormat="1" spans="1:7">
       <c r="B4" s="2">
         <v>10001</v>
       </c>
@@ -1317,7 +1327,10 @@
         <v>100</v>
       </c>
       <c r="F4" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G4" s="2">
+        <v>8000</v>
       </c>
     </row>
   </sheetData>

--- a/data/config/luban/config/general/develop.xlsx
+++ b/data/config/luban/config/general/develop.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$F$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1247,8 +1247,8 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="3" outlineLevelCol="6"/>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="32.8833333333333" style="2" customWidth="1"/>
     <col min="2" max="2" width="18.125" style="2" customWidth="1"/>
@@ -1315,42 +1315,94 @@
     </row>
     <row r="4" s="2" customFormat="1" spans="1:7">
       <c r="B4" s="2">
-        <v>10001</v>
+        <v>1010000</v>
       </c>
       <c r="C4" s="2">
+        <f>IF(B4="","",INT(B4/1000000))</f>
         <v>1</v>
       </c>
       <c r="D4" s="2">
+        <f>IF(B4="","",MOD(INT(B4/10000),100))</f>
         <v>1</v>
       </c>
       <c r="E4" s="2">
         <v>100</v>
       </c>
       <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="B5" s="2">
+        <v>2010000</v>
+      </c>
+      <c r="C5" s="2">
+        <f>IF(B5="","",INT(B5/1000000))</f>
+        <v>2</v>
+      </c>
+      <c r="D5" s="2">
+        <f>IF(B5="","",MOD(INT(B5/10000),100))</f>
         <v>1</v>
       </c>
-      <c r="G4" s="2">
+      <c r="E5" s="2">
+        <v>100</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="B6" s="2">
+        <v>3010000</v>
+      </c>
+      <c r="C6" s="2">
+        <f>IF(B6="","",INT(B6/1000000))</f>
+        <v>3</v>
+      </c>
+      <c r="D6" s="2">
+        <f>IF(B6="","",MOD(INT(B6/10000),100))</f>
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>100</v>
+      </c>
+      <c r="F6" s="2">
+        <v>2</v>
+      </c>
+      <c r="G6" s="2">
         <v>8000</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:F4" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:F6" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="D3">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3">
+  <conditionalFormatting sqref="F3">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3">
+  <conditionalFormatting sqref="B6">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B2 B5:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="89"/>
+  <conditionalFormatting sqref="B1:B2 B7:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="91"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data/config/luban/config/general/develop.xlsx
+++ b/data/config/luban/config/general/develop.xlsx
@@ -1247,8 +1247,8 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="5" outlineLevelCol="6"/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="6" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="32.8833333333333" style="2" customWidth="1"/>
     <col min="2" max="2" width="18.125" style="2" customWidth="1"/>
@@ -1379,30 +1379,55 @@
         <v>8000</v>
       </c>
     </row>
+    <row r="7" spans="1:7">
+      <c r="B7" s="2">
+        <v>4010000</v>
+      </c>
+      <c r="C7" s="2">
+        <f>IF(B7="","",INT(B7/1000000))</f>
+        <v>4</v>
+      </c>
+      <c r="D7" s="2">
+        <f>IF(B7="","",MOD(INT(B7/10000),100))</f>
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>100</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>10000</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:F6" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="D3">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3">
+  <conditionalFormatting sqref="B4">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5">
+  <conditionalFormatting sqref="B6">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
+  <conditionalFormatting sqref="B7">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B2 B7:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="91"/>
+  <conditionalFormatting sqref="B1:B2 B8:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="92"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
